--- a/docs/files/REPORT_FILTRI/Agente Cali Giuseppe - CR PASTORE PIERLUIGI.xlsx
+++ b/docs/files/REPORT_FILTRI/Agente Cali Giuseppe - CR PASTORE PIERLUIGI.xlsx
@@ -684,13 +684,13 @@
         <v>7</v>
       </c>
       <c r="B7" s="8" t="n">
-        <v>1598</v>
+        <v>1621</v>
       </c>
       <c r="C7" s="9" t="n">
-        <v>1342</v>
+        <v>0</v>
       </c>
       <c r="D7" s="10" t="n">
-        <v>422</v>
+        <v>410</v>
       </c>
       <c r="E7" s="2" t="n"/>
       <c r="F7" s="2" t="n"/>
@@ -842,19 +842,19 @@
         </is>
       </c>
       <c r="F11" s="12" t="n">
-        <v>346</v>
+        <v>342</v>
       </c>
       <c r="G11" s="12" t="n">
-        <v>394</v>
+        <v>383</v>
       </c>
       <c r="H11" s="12" t="n">
-        <v>87</v>
+        <v>80</v>
       </c>
       <c r="I11" s="12" t="n">
         <v>54</v>
       </c>
       <c r="J11" s="12" t="n">
-        <v>301</v>
+        <v>0</v>
       </c>
       <c r="K11" s="12" t="n">
         <v>130</v>
@@ -863,7 +863,7 @@
         <v>41</v>
       </c>
       <c r="M11" s="12" t="n">
-        <v>377</v>
+        <v>366</v>
       </c>
       <c r="N11" s="12" t="n">
         <v>3</v>
@@ -901,10 +901,10 @@
         </is>
       </c>
       <c r="F12" s="12" t="n">
-        <v>278</v>
+        <v>281</v>
       </c>
       <c r="G12" s="12" t="n">
-        <v>435</v>
+        <v>420</v>
       </c>
       <c r="H12" s="12" t="n">
         <v>14</v>
@@ -913,7 +913,7 @@
         <v>6</v>
       </c>
       <c r="J12" s="12" t="n">
-        <v>230</v>
+        <v>0</v>
       </c>
       <c r="K12" s="12" t="n">
         <v>67</v>
@@ -922,7 +922,7 @@
         <v>51</v>
       </c>
       <c r="M12" s="12" t="n">
-        <v>402</v>
+        <v>393</v>
       </c>
       <c r="N12" s="12" t="n">
         <v>6</v>
@@ -960,19 +960,19 @@
         </is>
       </c>
       <c r="F13" s="12" t="n">
-        <v>262</v>
+        <v>271</v>
       </c>
       <c r="G13" s="12" t="n">
-        <v>257</v>
+        <v>253</v>
       </c>
       <c r="H13" s="12" t="n">
         <v>43</v>
       </c>
       <c r="I13" s="12" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="J13" s="12" t="n">
-        <v>234</v>
+        <v>0</v>
       </c>
       <c r="K13" s="12" t="n">
         <v>108</v>
@@ -981,14 +981,14 @@
         <v>37</v>
       </c>
       <c r="M13" s="12" t="n">
-        <v>468</v>
+        <v>462</v>
       </c>
       <c r="N13" s="12" t="n">
         <v>7</v>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -1019,19 +1019,19 @@
         </is>
       </c>
       <c r="F14" s="12" t="n">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="G14" s="12" t="n">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="H14" s="12" t="n">
-        <v>123</v>
+        <v>118</v>
       </c>
       <c r="I14" s="12" t="n">
         <v>86</v>
       </c>
       <c r="J14" s="12" t="n">
-        <v>238</v>
+        <v>0</v>
       </c>
       <c r="K14" s="12" t="n">
         <v>113</v>
@@ -1040,10 +1040,10 @@
         <v>14</v>
       </c>
       <c r="M14" s="12" t="n">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="N14" s="12" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
@@ -1078,10 +1078,10 @@
         </is>
       </c>
       <c r="F15" s="12" t="n">
-        <v>236</v>
+        <v>247</v>
       </c>
       <c r="G15" s="12" t="n">
-        <v>264</v>
+        <v>261</v>
       </c>
       <c r="H15" s="12" t="n">
         <v>47</v>
@@ -1090,7 +1090,7 @@
         <v>25</v>
       </c>
       <c r="J15" s="12" t="n">
-        <v>171</v>
+        <v>0</v>
       </c>
       <c r="K15" s="12" t="n">
         <v>69</v>
@@ -1099,7 +1099,7 @@
         <v>76</v>
       </c>
       <c r="M15" s="12" t="n">
-        <v>408</v>
+        <v>402</v>
       </c>
       <c r="N15" s="12" t="n">
         <v>21</v>
@@ -1113,7 +1113,7 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>08063</t>
+          <t>08146</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
@@ -1123,7 +1123,7 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>STADERA POGGIOREALE</t>
+          <t>VIALE MADDALENA</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
@@ -1137,42 +1137,42 @@
         </is>
       </c>
       <c r="F16" s="12" t="n">
-        <v>113</v>
+        <v>117</v>
       </c>
       <c r="G16" s="12" t="n">
-        <v>73</v>
+        <v>169</v>
       </c>
       <c r="H16" s="12" t="n">
-        <v>49</v>
+        <v>59</v>
       </c>
       <c r="I16" s="12" t="n">
-        <v>18</v>
+        <v>101</v>
       </c>
       <c r="J16" s="12" t="n">
-        <v>101</v>
+        <v>0</v>
       </c>
       <c r="K16" s="12" t="n">
-        <v>55</v>
+        <v>25</v>
       </c>
       <c r="L16" s="12" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="M16" s="12" t="n">
-        <v>111</v>
+        <v>165</v>
       </c>
       <c r="N16" s="12" t="n">
-        <v>68</v>
+        <v>1</v>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>08146</t>
+          <t>08063</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
@@ -1182,7 +1182,7 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>VIALE MADDALENA</t>
+          <t>STADERA POGGIOREALE</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
@@ -1196,35 +1196,35 @@
         </is>
       </c>
       <c r="F17" s="12" t="n">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="G17" s="12" t="n">
-        <v>170</v>
+        <v>70</v>
       </c>
       <c r="H17" s="12" t="n">
-        <v>59</v>
+        <v>49</v>
       </c>
       <c r="I17" s="12" t="n">
-        <v>102</v>
+        <v>18</v>
       </c>
       <c r="J17" s="12" t="n">
-        <v>67</v>
+        <v>0</v>
       </c>
       <c r="K17" s="12" t="n">
-        <v>25</v>
+        <v>55</v>
       </c>
       <c r="L17" s="12" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="M17" s="12" t="n">
-        <v>168</v>
+        <v>111</v>
       </c>
       <c r="N17" s="12" t="n">
-        <v>1</v>
+        <v>68</v>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
